--- a/sources/3A_Manha_2_Bimestre.xlsx
+++ b/sources/3A_Manha_2_Bimestre.xlsx
@@ -61,7 +61,7 @@
     <x:t>Conselho Segundo Bimestre</x:t>
   </x:si>
   <x:si>
-    <x:t>272</x:t>
+    <x:t>342</x:t>
   </x:si>
   <x:si>
     <x:t>0 (Soma de todas as eletivas)</x:t>
@@ -186,201 +186,204 @@
     <x:t>17</x:t>
   </x:si>
   <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>85%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>87%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALESSANDRO TOMAZ DE LIMA JUNIOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA LUIZA MOLICA ROCHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARBARAH DUMONT SARAIVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>95%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>97%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRYAN VIEIRA ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>90%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARLOS FELIPE ALVES SOUZA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baixa - Transferência</x:t>
+  </x:si>
+  <x:si>
     <x:t>-</x:t>
   </x:si>
   <x:si>
-    <x:t>1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>84%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>87%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ALESSANDRO TOMAZ DE LIMA JUNIOR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>88%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANA LUIZA MOLICA ROCHA</x:t>
+    <x:t>100%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>98%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CAROLINE DOS ANJOS TEIXEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAVI CHALEGRA BARBOSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>76%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DAVID HENRIQUE DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>59%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDUARDO KENNEDY BELARMINO DOS SANTOS RAMOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELOAH DE AZEVEDO BARBOZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>93%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMANUELE CAROLINE MARTINS DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EMILY GABRIELLA BRITO DE CARVALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EVELYN RAYANE MENEZES DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>86%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GABRIELL ALCANTARA SATIRO DOS SANTOS</x:t>
   </x:si>
   <x:si>
     <x:t>89%</x:t>
   </x:si>
   <x:si>
-    <x:t>BARBARAH DUMONT SARAIVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>95%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>97%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BRYAN VIEIRA ALVES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARLOS FELIPE ALVES SOUZA DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Baixa - Transferência</x:t>
-  </x:si>
-  <x:si>
-    <x:t>100%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>98%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CAROLINE DOS ANJOS TEIXEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73%</x:t>
+    <x:t>GIOVANNA GUIMARÃES GOMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>99%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISABELLA FERNANDA DOS SANTOS PRADO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ISAQUE MENDES FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JONATHAS ALEXANDRE DIAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS ARAUJO CAMARGO DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS MATEUS SANTANA MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS PEREIRA DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAYZA BELMIRO DE MENEZES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>78%</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIRELA MIYUKI XAVIER PLACIDO</x:t>
   </x:si>
   <x:si>
     <x:t>80%</x:t>
   </x:si>
   <x:si>
-    <x:t>DAVI CHALEGRA BARBOSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>82%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DAVID HENRIQUE DE OLIVEIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>60%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDUARDO KENNEDY BELARMINO DOS SANTOS RAMOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELOAH DE AZEVEDO BARBOZA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>93%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMANUELE CAROLINE MARTINS DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>90%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EMILY GABRIELLA BRITO DE CARVALHO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>86%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EVELYN RAYANE MENEZES DA SILVA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GABRIELL ALCANTARA SATIRO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GIOVANNA GUIMARÃES GOMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>99%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISABELLA FERNANDA DOS SANTOS PRADO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>85%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ISAQUE MENDES FERREIRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>81%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JONATHAS ALEXANDRE DIAS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS ARAUJO CAMARGO DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>94%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS MATEUS SANTANA MARQUES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LUCAS PEREIRA DOS SANTOS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>78%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MAYZA BELMIRO DE MENEZES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>76%</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIRELA MIYUKI XAVIER PLACIDO</x:t>
-  </x:si>
-  <x:si>
     <x:t>NATALY SIMOES FIGUEIREDO</x:t>
   </x:si>
   <x:si>
-    <x:t>79%</x:t>
-  </x:si>
-  <x:si>
     <x:t>NICOLE PADULA MANTO</x:t>
   </x:si>
   <x:si>
@@ -402,12 +405,12 @@
     <x:t>TERESA MBUMBA MABIKA BOCA</x:t>
   </x:si>
   <x:si>
+    <x:t>96%</x:t>
+  </x:si>
+  <x:si>
     <x:t>THAYNA DA SILVA SOUSA</x:t>
   </x:si>
   <x:si>
-    <x:t>77%</x:t>
-  </x:si>
-  <x:si>
     <x:t>WILDER MAMANI VENTURA</x:t>
   </x:si>
   <x:si>
@@ -426,7 +429,7 @@
     <x:t>Aulas Dadas: 33</x:t>
   </x:si>
   <x:si>
-    <x:t>Aulas Dadas: 0</x:t>
+    <x:t>Aulas Dadas: 50</x:t>
   </x:si>
   <x:si>
     <x:t>Aulas Dadas: 29</x:t>
@@ -1383,13 +1386,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="X13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA13" s="12">
         <x:v>1</x:v>
@@ -1434,7 +1437,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO13" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP13" s="12" t="s">
         <x:v>47</x:v>
@@ -1443,30 +1446,30 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="AR13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AT13" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU13" s="12">
-        <x:v>44</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AV13" s="12" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="AW13" s="12">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="AX13" s="12" t="s">
         <x:v>55</x:v>
-      </x:c>
-      <x:c r="AW13" s="12">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="AX13" s="12" t="s">
-        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:50">
       <x:c r="A14" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B14" s="12" t="s">
         <x:v>44</x:v>
@@ -1478,7 +1481,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F14" s="12" t="s">
         <x:v>47</x:v>
@@ -1493,7 +1496,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="J14" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="12">
         <x:v>2</x:v>
@@ -1514,7 +1517,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="Q14" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R14" s="12" t="s">
         <x:v>47</x:v>
@@ -1526,22 +1529,22 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="U14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="W14" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="X14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA14" s="12">
         <x:v>2</x:v>
@@ -1562,7 +1565,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AG14" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH14" s="12" t="s">
         <x:v>47</x:v>
@@ -1595,30 +1598,30 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AR14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT14" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU14" s="12">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="AV14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AW14" s="12">
-        <x:v>67</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AX14" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:50">
       <x:c r="A15" s="11" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B15" s="12" t="s">
         <x:v>44</x:v>
@@ -1630,7 +1633,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E15" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F15" s="12" t="s">
         <x:v>47</x:v>
@@ -1687,13 +1690,13 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="X15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA15" s="12">
         <x:v>3</x:v>
@@ -1738,7 +1741,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO15" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP15" s="12" t="s">
         <x:v>47</x:v>
@@ -1747,30 +1750,30 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="AR15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT15" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU15" s="12">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AV15" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW15" s="12">
-        <x:v>64</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="AX15" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:50">
       <x:c r="A16" s="11" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B16" s="12" t="s">
         <x:v>44</x:v>
@@ -1815,10 +1818,10 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P16" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="Q16" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="R16" s="12" t="s">
         <x:v>47</x:v>
@@ -1827,25 +1830,25 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="T16" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U16" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V16" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="W16" s="12">
         <x:v>4</x:v>
       </x:c>
       <x:c r="X16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y16" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="Z16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA16" s="12">
         <x:v>4</x:v>
@@ -1875,7 +1878,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AJ16" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AK16" s="12" t="s">
         <x:v>47</x:v>
@@ -1899,30 +1902,30 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AR16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AT16" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU16" s="12">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="AV16" s="12" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="AW16" s="12">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="AX16" s="12" t="s">
         <x:v>66</x:v>
-      </x:c>
-      <x:c r="AW16" s="12">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="AX16" s="12" t="s">
-        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:50">
       <x:c r="A17" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="12" t="s">
         <x:v>44</x:v>
@@ -1934,7 +1937,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F17" s="12" t="s">
         <x:v>47</x:v>
@@ -1943,7 +1946,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="H17" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I17" s="12" t="s">
         <x:v>46</x:v>
@@ -1970,7 +1973,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="Q17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R17" s="12" t="s">
         <x:v>47</x:v>
@@ -1985,19 +1988,19 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="V17" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="W17" s="12">
         <x:v>5</x:v>
       </x:c>
       <x:c r="X17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA17" s="12">
         <x:v>5</x:v>
@@ -2051,39 +2054,39 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="AR17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT17" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU17" s="12">
-        <x:v>36</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AV17" s="12" t="s">
-        <x:v>56</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW17" s="12">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="AX17" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:50">
       <x:c r="A18" s="11" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="B18" s="12" t="s">
         <x:v>70</x:v>
-      </x:c>
-      <x:c r="B18" s="12" t="s">
-        <x:v>71</x:v>
       </x:c>
       <x:c r="C18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E18" s="12" t="s">
         <x:v>47</x:v>
@@ -2095,7 +2098,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="H18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I18" s="12" t="s">
         <x:v>47</x:v>
@@ -2107,7 +2110,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="L18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M18" s="12" t="s">
         <x:v>47</x:v>
@@ -2119,7 +2122,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="P18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q18" s="12" t="s">
         <x:v>47</x:v>
@@ -2131,7 +2134,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="T18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="U18" s="12" t="s">
         <x:v>47</x:v>
@@ -2143,19 +2146,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="X18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Y18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA18" s="12">
         <x:v>6</x:v>
       </x:c>
       <x:c r="AB18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AC18" s="12" t="s">
         <x:v>47</x:v>
@@ -2167,7 +2170,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AF18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AG18" s="12" t="s">
         <x:v>47</x:v>
@@ -2179,7 +2182,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AJ18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AK18" s="12" t="s">
         <x:v>47</x:v>
@@ -2191,7 +2194,7 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AN18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AO18" s="12" t="s">
         <x:v>47</x:v>
@@ -2203,13 +2206,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="AR18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AS18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT18" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU18" s="12">
         <x:v>0</x:v>
@@ -2238,7 +2241,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E19" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F19" s="12" t="s">
         <x:v>47</x:v>
@@ -2295,13 +2298,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="X19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA19" s="12">
         <x:v>7</x:v>
@@ -2346,7 +2349,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AO19" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AP19" s="12" t="s">
         <x:v>47</x:v>
@@ -2355,22 +2358,22 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="AR19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT19" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU19" s="12">
-        <x:v>74</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="AV19" s="12" t="s">
         <x:v>78</x:v>
       </x:c>
       <x:c r="AW19" s="12">
-        <x:v>116</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="AX19" s="12" t="s">
         <x:v>79</x:v>
@@ -2399,7 +2402,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="H20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I20" s="12" t="s">
         <x:v>50</x:v>
@@ -2414,7 +2417,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="M20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="N20" s="12" t="s">
         <x:v>47</x:v>
@@ -2423,10 +2426,10 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="P20" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R20" s="12" t="s">
         <x:v>47</x:v>
@@ -2438,22 +2441,22 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="U20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V20" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="W20" s="12">
         <x:v>8</x:v>
       </x:c>
       <x:c r="X20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA20" s="12">
         <x:v>8</x:v>
@@ -2474,7 +2477,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AG20" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AH20" s="12" t="s">
         <x:v>47</x:v>
@@ -2507,30 +2510,30 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="AR20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT20" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU20" s="12">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AV20" s="12" t="s">
-        <x:v>78</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AW20" s="12">
-        <x:v>101</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="AX20" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:50">
       <x:c r="A21" s="11" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B21" s="12" t="s">
         <x:v>44</x:v>
@@ -2551,10 +2554,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="H21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I21" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="J21" s="12" t="s">
         <x:v>47</x:v>
@@ -2566,7 +2569,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M21" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="N21" s="12" t="s">
         <x:v>47</x:v>
@@ -2575,7 +2578,7 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="P21" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q21" s="12" t="s">
         <x:v>75</x:v>
@@ -2590,7 +2593,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="U21" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="V21" s="12" t="s">
         <x:v>47</x:v>
@@ -2599,13 +2602,13 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="X21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="Z21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA21" s="12">
         <x:v>9</x:v>
@@ -2614,7 +2617,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="AC21" s="12" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="AD21" s="12" t="s">
         <x:v>47</x:v>
@@ -2623,10 +2626,10 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AF21" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AG21" s="12" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="AH21" s="12" t="s">
         <x:v>47</x:v>
@@ -2638,7 +2641,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="AK21" s="12" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="AL21" s="12" t="s">
         <x:v>47</x:v>
@@ -2659,30 +2662,30 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="AR21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AT21" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU21" s="12">
-        <x:v>145</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="AV21" s="12" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AW21" s="12">
-        <x:v>229</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="AX21" s="12" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:50">
       <x:c r="A22" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="12" t="s">
         <x:v>44</x:v>
@@ -2730,7 +2733,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="Q22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R22" s="12" t="s">
         <x:v>47</x:v>
@@ -2751,13 +2754,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="X22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA22" s="12">
         <x:v>10</x:v>
@@ -2766,7 +2769,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AC22" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD22" s="12" t="s">
         <x:v>47</x:v>
@@ -2775,7 +2778,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AF22" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AG22" s="12" t="s">
         <x:v>51</x:v>
@@ -2811,25 +2814,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="AR22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT22" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU22" s="12">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="AV22" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW22" s="12">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="AX22" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:50">
@@ -2882,7 +2885,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="Q23" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="R23" s="12" t="s">
         <x:v>47</x:v>
@@ -2891,7 +2894,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="T23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U23" s="12" t="s">
         <x:v>47</x:v>
@@ -2903,13 +2906,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="X23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y23" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="Z23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA23" s="12">
         <x:v>11</x:v>
@@ -2927,7 +2930,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AF23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AG23" s="12" t="s">
         <x:v>46</x:v>
@@ -2939,7 +2942,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AJ23" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AK23" s="12" t="s">
         <x:v>47</x:v>
@@ -2951,7 +2954,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AN23" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO23" s="12" t="s">
         <x:v>51</x:v>
@@ -2963,22 +2966,22 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="AR23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AS23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT23" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU23" s="12">
-        <x:v>13</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="AV23" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW23" s="12">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AX23" s="12" t="s">
         <x:v>93</x:v>
@@ -2998,7 +3001,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E24" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F24" s="12" t="s">
         <x:v>47</x:v>
@@ -3019,7 +3022,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="L24" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M24" s="12" t="s">
         <x:v>46</x:v>
@@ -3043,10 +3046,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="T24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="U24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V24" s="12" t="s">
         <x:v>47</x:v>
@@ -3055,13 +3058,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="X24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA24" s="12">
         <x:v>12</x:v>
@@ -3082,7 +3085,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AG24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AH24" s="12" t="s">
         <x:v>47</x:v>
@@ -3091,7 +3094,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AJ24" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AK24" s="12" t="s">
         <x:v>46</x:v>
@@ -3106,7 +3109,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO24" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP24" s="12" t="s">
         <x:v>47</x:v>
@@ -3115,30 +3118,30 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="AR24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT24" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU24" s="12">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="AV24" s="12" t="s">
         <x:v>95</x:v>
       </x:c>
       <x:c r="AW24" s="12">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="AX24" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:50">
       <x:c r="A25" s="11" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="12" t="s">
         <x:v>44</x:v>
@@ -3207,13 +3210,13 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="X25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Z25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA25" s="12">
         <x:v>13</x:v>
@@ -3231,7 +3234,7 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AF25" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AG25" s="12" t="s">
         <x:v>49</x:v>
@@ -3267,25 +3270,25 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="AR25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AT25" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU25" s="12">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AV25" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AW25" s="12">
-        <x:v>71</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AX25" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:50">
@@ -3302,7 +3305,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E26" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F26" s="12" t="s">
         <x:v>47</x:v>
@@ -3317,7 +3320,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="J26" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K26" s="12">
         <x:v>14</x:v>
@@ -3359,13 +3362,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="X26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Y26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Z26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA26" s="12">
         <x:v>14</x:v>
@@ -3419,30 +3422,30 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="AR26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT26" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU26" s="12">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AV26" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AW26" s="12">
-        <x:v>70</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="AX26" s="12" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:50">
       <x:c r="A27" s="11" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B27" s="12" t="s">
         <x:v>44</x:v>
@@ -3511,13 +3514,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="X27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA27" s="12">
         <x:v>15</x:v>
@@ -3526,7 +3529,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AC27" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AD27" s="12" t="s">
         <x:v>47</x:v>
@@ -3571,30 +3574,30 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="AR27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT27" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU27" s="12">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="AV27" s="12" t="s">
-        <x:v>97</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="AW27" s="12">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AX27" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>101</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:50">
       <x:c r="A28" s="11" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B28" s="12" t="s">
         <x:v>44</x:v>
@@ -3651,7 +3654,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="T28" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U28" s="12" t="s">
         <x:v>47</x:v>
@@ -3663,13 +3666,13 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="X28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA28" s="12">
         <x:v>16</x:v>
@@ -3723,19 +3726,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="AR28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT28" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU28" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV28" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW28" s="12">
         <x:v>2</x:v>
@@ -3746,7 +3749,7 @@
     </x:row>
     <x:row r="29" spans="1:50">
       <x:c r="A29" s="11" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B29" s="12" t="s">
         <x:v>44</x:v>
@@ -3758,7 +3761,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E29" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F29" s="12" t="s">
         <x:v>47</x:v>
@@ -3794,7 +3797,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="Q29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="R29" s="12" t="s">
         <x:v>47</x:v>
@@ -3803,10 +3806,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="T29" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U29" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V29" s="12" t="s">
         <x:v>47</x:v>
@@ -3815,13 +3818,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="X29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="Z29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA29" s="12">
         <x:v>17</x:v>
@@ -3875,30 +3878,30 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="AR29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT29" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU29" s="12">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="AV29" s="12" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AW29" s="12">
-        <x:v>62</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="AX29" s="12" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:50">
       <x:c r="A30" s="11" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="12" t="s">
         <x:v>44</x:v>
@@ -3925,7 +3928,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="J30" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="K30" s="12">
         <x:v>18</x:v>
@@ -3967,13 +3970,13 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="X30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA30" s="12">
         <x:v>18</x:v>
@@ -4018,7 +4021,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO30" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AP30" s="12" t="s">
         <x:v>47</x:v>
@@ -4027,30 +4030,30 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="AR30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS30" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AT30" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU30" s="12">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AV30" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW30" s="12">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="AX30" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:50">
       <x:c r="A31" s="11" t="s">
-        <x:v>106</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B31" s="12" t="s">
         <x:v>44</x:v>
@@ -4083,7 +4086,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="L31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="M31" s="12" t="s">
         <x:v>47</x:v>
@@ -4107,7 +4110,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="T31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U31" s="12" t="s">
         <x:v>47</x:v>
@@ -4119,13 +4122,13 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="X31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA31" s="12">
         <x:v>19</x:v>
@@ -4155,7 +4158,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AJ31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK31" s="12" t="s">
         <x:v>47</x:v>
@@ -4167,7 +4170,7 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AN31" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO31" s="12" t="s">
         <x:v>47</x:v>
@@ -4179,19 +4182,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="AR31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AS31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT31" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU31" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV31" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW31" s="12">
         <x:v>2</x:v>
@@ -4202,7 +4205,7 @@
     </x:row>
     <x:row r="32" spans="1:50">
       <x:c r="A32" s="11" t="s">
-        <x:v>107</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B32" s="12" t="s">
         <x:v>44</x:v>
@@ -4271,13 +4274,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="X32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA32" s="12">
         <x:v>20</x:v>
@@ -4331,30 +4334,30 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="AR32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT32" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU32" s="12">
         <x:v>17</x:v>
       </x:c>
       <x:c r="AV32" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="AW32" s="12">
         <x:v>31</x:v>
       </x:c>
       <x:c r="AX32" s="12" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:50">
       <x:c r="A33" s="11" t="s">
-        <x:v>109</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B33" s="12" t="s">
         <x:v>44</x:v>
@@ -4423,13 +4426,13 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="X33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA33" s="12">
         <x:v>21</x:v>
@@ -4483,19 +4486,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="AR33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="AS33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT33" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU33" s="12">
         <x:v>2</x:v>
       </x:c>
       <x:c r="AV33" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="AW33" s="12">
         <x:v>2</x:v>
@@ -4506,7 +4509,7 @@
     </x:row>
     <x:row r="34" spans="1:50">
       <x:c r="A34" s="11" t="s">
-        <x:v>110</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B34" s="12" t="s">
         <x:v>44</x:v>
@@ -4527,7 +4530,7 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="H34" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I34" s="12" t="s">
         <x:v>46</x:v>
@@ -4542,7 +4545,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M34" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N34" s="12" t="s">
         <x:v>47</x:v>
@@ -4554,7 +4557,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="Q34" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="R34" s="12" t="s">
         <x:v>47</x:v>
@@ -4566,7 +4569,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="U34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="V34" s="12" t="s">
         <x:v>47</x:v>
@@ -4575,13 +4578,13 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="X34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="Z34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA34" s="12">
         <x:v>22</x:v>
@@ -4590,7 +4593,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AC34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AD34" s="12" t="s">
         <x:v>47</x:v>
@@ -4614,7 +4617,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AK34" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AL34" s="12" t="s">
         <x:v>47</x:v>
@@ -4626,7 +4629,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO34" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AP34" s="12" t="s">
         <x:v>47</x:v>
@@ -4635,30 +4638,30 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="AR34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT34" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU34" s="12">
-        <x:v>80</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="AV34" s="12" t="s">
-        <x:v>111</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="AW34" s="12">
-        <x:v>127</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="AX34" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>113</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:50">
       <x:c r="A35" s="11" t="s">
-        <x:v>113</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B35" s="12" t="s">
         <x:v>44</x:v>
@@ -4670,7 +4673,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="E35" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F35" s="12" t="s">
         <x:v>47</x:v>
@@ -4679,7 +4682,7 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="H35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I35" s="12" t="s">
         <x:v>51</x:v>
@@ -4718,7 +4721,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="U35" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V35" s="12" t="s">
         <x:v>47</x:v>
@@ -4727,13 +4730,13 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="X35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA35" s="12">
         <x:v>23</x:v>
@@ -4754,7 +4757,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AG35" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AH35" s="12" t="s">
         <x:v>47</x:v>
@@ -4787,30 +4790,30 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="AR35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AS35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AT35" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU35" s="12">
-        <x:v>64</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="AV35" s="12" t="s">
-        <x:v>114</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="AW35" s="12">
-        <x:v>128</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="AX35" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:50">
       <x:c r="A36" s="11" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B36" s="12" t="s">
         <x:v>44</x:v>
@@ -4822,7 +4825,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="E36" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F36" s="12" t="s">
         <x:v>47</x:v>
@@ -4843,7 +4846,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="L36" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="M36" s="12" t="s">
         <x:v>46</x:v>
@@ -4879,13 +4882,13 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="X36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA36" s="12">
         <x:v>24</x:v>
@@ -4894,7 +4897,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC36" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AD36" s="12" t="s">
         <x:v>47</x:v>
@@ -4906,7 +4909,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AG36" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="AH36" s="12" t="s">
         <x:v>47</x:v>
@@ -4930,7 +4933,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO36" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP36" s="12" t="s">
         <x:v>47</x:v>
@@ -4939,30 +4942,30 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="AR36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AT36" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU36" s="12">
-        <x:v>53</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="AV36" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="AW36" s="12">
-        <x:v>125</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="AX36" s="12" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:50">
       <x:c r="A37" s="11" t="s">
-        <x:v>116</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B37" s="12" t="s">
         <x:v>44</x:v>
@@ -4998,7 +5001,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="M37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="N37" s="12" t="s">
         <x:v>47</x:v>
@@ -5007,7 +5010,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="P37" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="Q37" s="12" t="s">
         <x:v>49</x:v>
@@ -5022,7 +5025,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="U37" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="V37" s="12" t="s">
         <x:v>47</x:v>
@@ -5031,22 +5034,22 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="X37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="Z37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA37" s="12">
         <x:v>25</x:v>
       </x:c>
       <x:c r="AB37" s="12" t="s">
-        <x:v>49</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AC37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD37" s="12" t="s">
         <x:v>47</x:v>
@@ -5058,7 +5061,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AG37" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AH37" s="12" t="s">
         <x:v>47</x:v>
@@ -5091,42 +5094,42 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="AR37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="AT37" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU37" s="12">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AV37" s="12" t="s">
-        <x:v>117</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="AW37" s="12">
-        <x:v>93</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="AX37" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:50">
       <x:c r="A38" s="11" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B38" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D38" s="12" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E38" s="12" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E38" s="12" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="F38" s="12" t="s">
         <x:v>47</x:v>
@@ -5147,7 +5150,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="L38" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="M38" s="12" t="s">
         <x:v>49</x:v>
@@ -5159,7 +5162,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="P38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q38" s="12" t="s">
         <x:v>49</x:v>
@@ -5183,19 +5186,19 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="X38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Y38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA38" s="12">
         <x:v>26</x:v>
       </x:c>
       <x:c r="AB38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AC38" s="12" t="s">
         <x:v>75</x:v>
@@ -5207,10 +5210,10 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AF38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AG38" s="12" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="AH38" s="12" t="s">
         <x:v>47</x:v>
@@ -5231,7 +5234,7 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AN38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AO38" s="12" t="s">
         <x:v>49</x:v>
@@ -5243,30 +5246,30 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="AR38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AS38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AT38" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU38" s="12">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="AV38" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AW38" s="12">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AX38" s="12" t="s">
-        <x:v>91</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:50">
       <x:c r="A39" s="11" t="s">
-        <x:v>120</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B39" s="12" t="s">
         <x:v>44</x:v>
@@ -5293,7 +5296,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="J39" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K39" s="12">
         <x:v>27</x:v>
@@ -5323,7 +5326,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="T39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U39" s="12" t="s">
         <x:v>49</x:v>
@@ -5335,13 +5338,13 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="X39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA39" s="12">
         <x:v>27</x:v>
@@ -5350,7 +5353,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AC39" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD39" s="12" t="s">
         <x:v>47</x:v>
@@ -5371,7 +5374,7 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AJ39" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK39" s="12" t="s">
         <x:v>51</x:v>
@@ -5395,30 +5398,30 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="AR39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT39" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU39" s="12">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AV39" s="12" t="s">
-        <x:v>69</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="AW39" s="12">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="AX39" s="12" t="s">
-        <x:v>95</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:50">
       <x:c r="A40" s="11" t="s">
-        <x:v>121</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B40" s="12" t="s">
         <x:v>44</x:v>
@@ -5430,7 +5433,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E40" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F40" s="12" t="s">
         <x:v>47</x:v>
@@ -5439,7 +5442,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="H40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I40" s="12" t="s">
         <x:v>49</x:v>
@@ -5478,7 +5481,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="U40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="V40" s="12" t="s">
         <x:v>47</x:v>
@@ -5487,13 +5490,13 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="X40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="Y40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="Z40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA40" s="12">
         <x:v>28</x:v>
@@ -5502,7 +5505,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="AC40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AD40" s="12" t="s">
         <x:v>47</x:v>
@@ -5514,7 +5517,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AG40" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AH40" s="12" t="s">
         <x:v>47</x:v>
@@ -5523,7 +5526,7 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AJ40" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AK40" s="12" t="s">
         <x:v>51</x:v>
@@ -5538,7 +5541,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="AO40" s="12" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="AP40" s="12" t="s">
         <x:v>47</x:v>
@@ -5547,30 +5550,30 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="AR40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AS40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AT40" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU40" s="12">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AV40" s="12" t="s">
-        <x:v>105</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="AW40" s="12">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="AX40" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:50">
       <x:c r="A41" s="11" t="s">
-        <x:v>122</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B41" s="12" t="s">
         <x:v>44</x:v>
@@ -5582,7 +5585,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="E41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F41" s="12" t="s">
         <x:v>47</x:v>
@@ -5639,13 +5642,13 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="X41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA41" s="12">
         <x:v>29</x:v>
@@ -5654,7 +5657,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AC41" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD41" s="12" t="s">
         <x:v>47</x:v>
@@ -5690,7 +5693,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="AO41" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="AP41" s="12" t="s">
         <x:v>47</x:v>
@@ -5699,39 +5702,39 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="AR41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="AS41" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="AT41" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU41" s="12">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AV41" s="12" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="AW41" s="12">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="AX41" s="12" t="s">
-        <x:v>55</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:50">
       <x:c r="A42" s="11" t="s">
-        <x:v>123</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B42" s="12" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E42" s="12" t="s">
         <x:v>47</x:v>
@@ -5743,7 +5746,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I42" s="12" t="s">
         <x:v>47</x:v>
@@ -5755,7 +5758,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="L42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M42" s="12" t="s">
         <x:v>47</x:v>
@@ -5767,7 +5770,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="P42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q42" s="12" t="s">
         <x:v>47</x:v>
@@ -5779,7 +5782,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="T42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="U42" s="12" t="s">
         <x:v>47</x:v>
@@ -5791,19 +5794,19 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="X42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Y42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA42" s="12">
         <x:v>30</x:v>
       </x:c>
       <x:c r="AB42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AC42" s="12" t="s">
         <x:v>47</x:v>
@@ -5815,7 +5818,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AF42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AG42" s="12" t="s">
         <x:v>47</x:v>
@@ -5827,7 +5830,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AJ42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AK42" s="12" t="s">
         <x:v>47</x:v>
@@ -5839,7 +5842,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AN42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AO42" s="12" t="s">
         <x:v>47</x:v>
@@ -5851,13 +5854,13 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="AR42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AS42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT42" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU42" s="12">
         <x:v>0</x:v>
@@ -5869,12 +5872,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="AX42" s="12" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:50">
       <x:c r="A43" s="11" t="s">
-        <x:v>124</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B43" s="12" t="s">
         <x:v>44</x:v>
@@ -5883,7 +5886,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="D43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E43" s="12" t="s">
         <x:v>47</x:v>
@@ -5895,7 +5898,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="I43" s="12" t="s">
         <x:v>47</x:v>
@@ -5931,10 +5934,10 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="T43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="U43" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="V43" s="12" t="s">
         <x:v>47</x:v>
@@ -5943,13 +5946,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="X43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Y43" s="12" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="Z43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA43" s="12">
         <x:v>31</x:v>
@@ -5958,7 +5961,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC43" s="12" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="AD43" s="12" t="s">
         <x:v>47</x:v>
@@ -5979,7 +5982,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AJ43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AK43" s="12" t="s">
         <x:v>47</x:v>
@@ -5991,7 +5994,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AN43" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AO43" s="12" t="s">
         <x:v>51</x:v>
@@ -6003,30 +6006,30 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="AR43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="AT43" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU43" s="12">
-        <x:v>16</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="AV43" s="12" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="AW43" s="12">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="AX43" s="12" t="s">
-        <x:v>67</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:50">
       <x:c r="A44" s="11" t="s">
-        <x:v>125</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B44" s="12" t="s">
         <x:v>44</x:v>
@@ -6038,7 +6041,7 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E44" s="12" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F44" s="12" t="s">
         <x:v>47</x:v>
@@ -6053,7 +6056,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="J44" s="12" t="s">
-        <x:v>83</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="K44" s="12">
         <x:v>32</x:v>
@@ -6095,13 +6098,13 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="X44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Y44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="Z44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA44" s="12">
         <x:v>32</x:v>
@@ -6110,7 +6113,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AC44" s="12" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="AD44" s="12" t="s">
         <x:v>47</x:v>
@@ -6119,10 +6122,10 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AF44" s="12" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="AG44" s="12" t="s">
         <x:v>58</x:v>
-      </x:c>
-      <x:c r="AG44" s="12" t="s">
-        <x:v>59</x:v>
       </x:c>
       <x:c r="AH44" s="12" t="s">
         <x:v>47</x:v>
@@ -6146,7 +6149,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="AO44" s="12" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="AP44" s="12" t="s">
         <x:v>47</x:v>
@@ -6155,39 +6158,39 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="AR44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AS44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="AT44" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU44" s="12">
-        <x:v>62</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AV44" s="12" t="s">
-        <x:v>126</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="AW44" s="12">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="AX44" s="12" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="AX44" s="12" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:50">
       <x:c r="A45" s="11" t="s">
-        <x:v>127</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B45" s="12" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="D45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E45" s="12" t="s">
         <x:v>47</x:v>
@@ -6199,7 +6202,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="H45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I45" s="12" t="s">
         <x:v>47</x:v>
@@ -6211,7 +6214,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="L45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="M45" s="12" t="s">
         <x:v>47</x:v>
@@ -6223,7 +6226,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="P45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Q45" s="12" t="s">
         <x:v>47</x:v>
@@ -6235,7 +6238,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="T45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="U45" s="12" t="s">
         <x:v>47</x:v>
@@ -6247,19 +6250,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="X45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="Y45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Z45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AA45" s="12">
         <x:v>33</x:v>
       </x:c>
       <x:c r="AB45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AC45" s="12" t="s">
         <x:v>47</x:v>
@@ -6271,7 +6274,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AF45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AG45" s="12" t="s">
         <x:v>47</x:v>
@@ -6283,7 +6286,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AJ45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AK45" s="12" t="s">
         <x:v>47</x:v>
@@ -6295,7 +6298,7 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AN45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AO45" s="12" t="s">
         <x:v>47</x:v>
@@ -6307,13 +6310,13 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="AR45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="AS45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AT45" s="12" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="AU45" s="12">
         <x:v>0</x:v>
@@ -6330,73 +6333,73 @@
     </x:row>
     <x:row r="46" spans="1:50">
       <x:c r="A46" s="13" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B46" s="13" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C46" s="7" t="s">
-        <x:v>129</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D46" s="7"/>
       <x:c r="E46" s="7"/>
       <x:c r="F46" s="7"/>
       <x:c r="G46" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H46" s="7"/>
       <x:c r="I46" s="7"/>
       <x:c r="J46" s="7"/>
       <x:c r="K46" s="7" t="s">
-        <x:v>130</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="L46" s="7"/>
       <x:c r="M46" s="7"/>
       <x:c r="N46" s="7"/>
       <x:c r="O46" s="7" t="s">
-        <x:v>131</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="P46" s="7"/>
       <x:c r="Q46" s="7"/>
       <x:c r="R46" s="7"/>
       <x:c r="S46" s="7" t="s">
-        <x:v>132</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="T46" s="7"/>
       <x:c r="U46" s="7"/>
       <x:c r="V46" s="7"/>
       <x:c r="W46" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="X46" s="7"/>
       <x:c r="Y46" s="7"/>
       <x:c r="Z46" s="7"/>
       <x:c r="AA46" s="7" t="s">
-        <x:v>134</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="AB46" s="7"/>
       <x:c r="AC46" s="7"/>
       <x:c r="AD46" s="7"/>
       <x:c r="AE46" s="7" t="s">
-        <x:v>135</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="AF46" s="7"/>
       <x:c r="AG46" s="7"/>
       <x:c r="AH46" s="7"/>
       <x:c r="AI46" s="7" t="s">
-        <x:v>136</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="AJ46" s="7"/>
       <x:c r="AK46" s="7"/>
       <x:c r="AL46" s="7"/>
       <x:c r="AM46" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="AN46" s="7"/>
       <x:c r="AO46" s="7"/>
       <x:c r="AP46" s="7"/>
       <x:c r="AQ46" s="7" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="AR46" s="7"/>
       <x:c r="AS46" s="7"/>
@@ -6408,37 +6411,37 @@
     </x:row>
     <x:row r="48" spans="1:50">
       <x:c r="A48" s="14" t="s">
-        <x:v>138</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:50">
       <x:c r="A49" s="13" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:50">
       <x:c r="A50" s="13" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:50">
       <x:c r="A51" s="13" t="s">
-        <x:v>141</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:50">
       <x:c r="A52" s="13" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:50">
       <x:c r="A53" s="13" t="s">
-        <x:v>143</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:50">
       <x:c r="A54" s="13" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
